--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Passive Multi-Asset Fund of Funds.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Passive Multi-Asset Fund of Funds.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="94">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Passive Multi-Asset Fund of Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -55,13 +55,13 @@
     <t/>
   </si>
   <si>
-    <t>SBI CPSE Bond Plus SDL Sep 2026 50:50 Index Fund - Direct – Growth</t>
-  </si>
-  <si>
-    <t>INF200KA13D5</t>
-  </si>
-  <si>
-    <t>Finance</t>
+    <t>ICICI Pru Nifty PSU Bond Plus SDL Sep 2027 40:60 Index Fund-Direct-Growth</t>
+  </si>
+  <si>
+    <t>INF109KC1S88</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
   </si>
   <si>
     <t>ICICI Prudential Nifty Bank ETF</t>
@@ -70,10 +70,7 @@
     <t>INF109KC15I8</t>
   </si>
   <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>ICICI Prudential S&amp;P BSE Liquid Rate ETF</t>
+    <t>ICICI Prudential BSE Liquid Rate ETF - IDCW</t>
   </si>
   <si>
     <t>INF109KC1KT9</t>
@@ -97,10 +94,28 @@
     <t>INF109KC18O0</t>
   </si>
   <si>
-    <t>Axis CRISIL IBX 70:30 CPSE Plus SDL April 2025 Index Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF846K015F2</t>
+    <t>ICICI Prudential Nifty IT ETF</t>
+  </si>
+  <si>
+    <t>INF109KC16I6</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Nifty Infrastructure ETF</t>
+  </si>
+  <si>
+    <t>INF109KC16E5</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Nifty 50 ETF</t>
+  </si>
+  <si>
+    <t>INF109K012R6</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Nifty Healthcare ETF</t>
+  </si>
+  <si>
+    <t>INF109KC1Q72</t>
   </si>
   <si>
     <t>ICICI Prudential Nifty FMCG ETF</t>
@@ -109,22 +124,34 @@
     <t>INF109KC19V3</t>
   </si>
   <si>
+    <t>BHARAT 22 ETF</t>
+  </si>
+  <si>
+    <t>INF109KB15Y7</t>
+  </si>
+  <si>
     <t>ICICI Prudential Nifty Oil &amp; Gas ETF</t>
   </si>
   <si>
     <t>INF109KC18W3</t>
   </si>
   <si>
-    <t>ICICI Prudential Gold ETF</t>
-  </si>
-  <si>
-    <t>INF109KC1NT3</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Healthcare ETF</t>
-  </si>
-  <si>
-    <t>INF109KC1Q72</t>
+    <t>ICICI Prudential Nifty Commodities ETF</t>
+  </si>
+  <si>
+    <t>INF109KC19O8</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Nifty Metal ETF</t>
+  </si>
+  <si>
+    <t>INF109KC19W1</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Nifty SDL Sep 2026 Index Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109KC13P8</t>
   </si>
   <si>
     <t>Reliance CPSE ETF</t>
@@ -133,60 +160,24 @@
     <t>INF457M01133</t>
   </si>
   <si>
-    <t>BHARAT 22 ETF</t>
-  </si>
-  <si>
-    <t>INF109KB15Y7</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Commodities ETF</t>
-  </si>
-  <si>
-    <t>INF109KC19O8</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Metal ETF</t>
-  </si>
-  <si>
-    <t>INF109KC19W1</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Infrastructure ETF</t>
-  </si>
-  <si>
-    <t>INF109KC16E5</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty IT ETF</t>
-  </si>
-  <si>
-    <t>INF109KC16I6</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty SDL Sep 2026 Index Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF109KC13P8</t>
-  </si>
-  <si>
     <t>Foreign Securities/Overseas ETFs</t>
   </si>
   <si>
+    <t>ISHARES MSCI JAPAN ETF</t>
+  </si>
+  <si>
+    <t>US46434G8226</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
     <t>ISHARES MSCI CHINA ETF</t>
   </si>
   <si>
     <t>US46429B6719</t>
   </si>
   <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>ISHARES MSCI JAPAN ETF</t>
-  </si>
-  <si>
-    <t>US46434G8226</t>
-  </si>
-  <si>
     <t>ISHARES GLOBAL CONSUMER STAPLE</t>
   </si>
   <si>
@@ -196,24 +187,24 @@
     <t>Aerospace &amp; Defense</t>
   </si>
   <si>
+    <t>ISHARES MSCI INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>US46434V4564</t>
+  </si>
+  <si>
+    <t>ISHARES LATIN AMERICA 40 ETF</t>
+  </si>
+  <si>
+    <t>US4642873909</t>
+  </si>
+  <si>
     <t>PROSHARES S&amp;P 500 DIVIDEND</t>
   </si>
   <si>
     <t>US74348A4673</t>
   </si>
   <si>
-    <t>ISHARES MSCI INTERNATIONAL</t>
-  </si>
-  <si>
-    <t>US46434V4564</t>
-  </si>
-  <si>
-    <t>ISHARES LATIN AMERICA 40 ETF</t>
-  </si>
-  <si>
-    <t>US4642873909</t>
-  </si>
-  <si>
     <t>VANECK GOLD MINERS ETF</t>
   </si>
   <si>
@@ -238,12 +229,6 @@
     <t>US4642873255</t>
   </si>
   <si>
-    <t>ISHARES GLOBAL FINANCIALS ETF</t>
-  </si>
-  <si>
-    <t>US4642873339</t>
-  </si>
-  <si>
     <t>ISHARES GLOBAL ENERGY ETF</t>
   </si>
   <si>
@@ -301,7 +286,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -311,9 +296,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - CRISIL Hybrid 50 + 50 - Moderate Index (80%) + S&amp;P Global 1200 Index (15%) + Domestic Gold Price (5%)</t>
   </si>
 </sst>
 </file>
@@ -638,13 +620,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -662,8 +644,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="13411200"/>
-          <a:ext cx="5353050" cy="1905000"/>
+          <a:off x="666750" y="13030200"/>
+          <a:ext cx="5334000" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -677,13 +659,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -701,8 +683,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="16268700"/>
-          <a:ext cx="5353050" cy="1905000"/>
+          <a:off x="666750" y="15887700"/>
+          <a:ext cx="5334000" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1035,11 +1017,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J82"/>
+  <dimension ref="B1:J79"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="24" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="24" width="80.28571428571429" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="24" width="80.0" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" style="24" width="16.857142857142858" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="24" width="22.428571428571427" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="24" width="12.285714285714286" collapsed="true"/>
@@ -1129,10 +1111,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="9">
-        <v>74750.77</v>
+        <v>77053.69</v>
       </c>
       <c r="G5" s="10">
-        <v>0.6736391145855</v>
+        <v>0.6733858210483</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>12</v>
@@ -1152,13 +1134,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="14">
-        <v>156193920.838</v>
+        <v>162631687.064</v>
       </c>
       <c r="F6" s="15">
-        <v>18564.90</v>
+        <v>20295.46</v>
       </c>
       <c r="G6" s="16">
-        <v>0.1673031969889</v>
+        <v>0.177365613453</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>12</v>
@@ -1175,16 +1157,16 @@
         <v>17</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" s="14">
-        <v>14028000</v>
+        <v>12998000</v>
       </c>
       <c r="F7" s="15">
-        <v>7068.71</v>
+        <v>7360.77</v>
       </c>
       <c r="G7" s="16">
-        <v>0.0637018126457</v>
+        <v>0.0643270705141</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>12</v>
@@ -1195,22 +1177,22 @@
     </row>
     <row r="8" spans="2:9" ht="15" customHeight="1">
       <c r="B8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="D8" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E8" s="14">
-        <v>500383.1633</v>
+        <v>547596.3143</v>
       </c>
       <c r="F8" s="15">
-        <v>5003.78</v>
+        <v>5475.91</v>
       </c>
       <c r="G8" s="16">
-        <v>0.0450930730049</v>
+        <v>0.0478549457052</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>12</v>
@@ -1221,22 +1203,22 @@
     </row>
     <row r="9" spans="2:9" ht="15" customHeight="1">
       <c r="B9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>22</v>
-      </c>
       <c r="D9" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E9" s="14">
-        <v>20262328</v>
+        <v>19002328</v>
       </c>
       <c r="F9" s="15">
-        <v>4966.30</v>
+        <v>5246.54</v>
       </c>
       <c r="G9" s="16">
-        <v>0.044755310678</v>
+        <v>0.0458504407195</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>12</v>
@@ -1247,22 +1229,22 @@
     </row>
     <row r="10" spans="2:9" ht="15" customHeight="1">
       <c r="B10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>24</v>
-      </c>
       <c r="D10" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E10" s="14">
         <v>8180000</v>
       </c>
       <c r="F10" s="15">
-        <v>4857.28</v>
+        <v>5120.68</v>
       </c>
       <c r="G10" s="16">
-        <v>0.0437728440589</v>
+        <v>0.0447505279257</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>12</v>
@@ -1273,22 +1255,22 @@
     </row>
     <row r="11" spans="2:9" ht="15" customHeight="1">
       <c r="B11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>26</v>
-      </c>
       <c r="D11" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E11" s="14">
-        <v>1846800</v>
+        <v>1896800</v>
       </c>
       <c r="F11" s="15">
-        <v>4546.08</v>
+        <v>4902.85</v>
       </c>
       <c r="G11" s="16">
-        <v>0.0409683713764</v>
+        <v>0.0428468730404</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>12</v>
@@ -1299,22 +1281,22 @@
     </row>
     <row r="12" spans="2:9" ht="15" customHeight="1">
       <c r="B12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>28</v>
-      </c>
       <c r="D12" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E12" s="14">
-        <v>37940861.766</v>
+        <v>11856080</v>
       </c>
       <c r="F12" s="15">
-        <v>4482.14</v>
+        <v>4788.67</v>
       </c>
       <c r="G12" s="16">
-        <v>0.0403921567771</v>
+        <v>0.0418490338319</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>12</v>
@@ -1325,22 +1307,22 @@
     </row>
     <row r="13" spans="2:9" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>30</v>
-      </c>
       <c r="D13" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E13" s="14">
-        <v>6908000</v>
+        <v>4334880</v>
       </c>
       <c r="F13" s="15">
-        <v>4104.73</v>
+        <v>3978.99</v>
       </c>
       <c r="G13" s="16">
-        <v>0.0369910127055</v>
+        <v>0.0347730971494</v>
       </c>
       <c r="H13" s="15" t="s">
         <v>12</v>
@@ -1351,22 +1333,22 @@
     </row>
     <row r="14" spans="2:9" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>32</v>
-      </c>
       <c r="D14" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E14" s="14">
-        <v>31147326</v>
+        <v>1239000</v>
       </c>
       <c r="F14" s="15">
-        <v>3310.96</v>
+        <v>3427.07</v>
       </c>
       <c r="G14" s="16">
-        <v>0.0298377148868</v>
+        <v>0.0299497706825</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>12</v>
@@ -1377,22 +1359,22 @@
     </row>
     <row r="15" spans="2:9" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>34</v>
-      </c>
       <c r="D15" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E15" s="14">
-        <v>4604585</v>
+        <v>2218531</v>
       </c>
       <c r="F15" s="15">
-        <v>3282.15</v>
+        <v>3151.20</v>
       </c>
       <c r="G15" s="16">
-        <v>0.0295780848804</v>
+        <v>0.0275388939749</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>12</v>
@@ -1403,22 +1385,22 @@
     </row>
     <row r="16" spans="2:9" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>36</v>
-      </c>
       <c r="D16" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E16" s="14">
-        <v>2182531</v>
+        <v>5038000</v>
       </c>
       <c r="F16" s="15">
-        <v>3070.38</v>
+        <v>2965.87</v>
       </c>
       <c r="G16" s="16">
-        <v>0.0276696556389</v>
+        <v>0.0259192623361</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>12</v>
@@ -1429,22 +1411,22 @@
     </row>
     <row r="17" spans="2:9" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>38</v>
-      </c>
       <c r="D17" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E17" s="14">
-        <v>2530500</v>
+        <v>2575000</v>
       </c>
       <c r="F17" s="15">
-        <v>2188.63</v>
+        <v>2812.93</v>
       </c>
       <c r="G17" s="16">
-        <v>0.0197234995085</v>
+        <v>0.0245826926342</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>12</v>
@@ -1455,22 +1437,22 @@
     </row>
     <row r="18" spans="2:9" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>40</v>
-      </c>
       <c r="D18" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E18" s="14">
-        <v>2000000</v>
+        <v>22922326</v>
       </c>
       <c r="F18" s="15">
-        <v>2095.80</v>
+        <v>2629.19</v>
       </c>
       <c r="G18" s="16">
-        <v>0.0188869339586</v>
+        <v>0.0229769562865</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>12</v>
@@ -1481,22 +1463,22 @@
     </row>
     <row r="19" spans="2:9" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>42</v>
-      </c>
       <c r="D19" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E19" s="14">
         <v>2060000</v>
       </c>
       <c r="F19" s="15">
-        <v>1684.46</v>
+        <v>1789.52</v>
       </c>
       <c r="G19" s="16">
-        <v>0.015180019456</v>
+        <v>0.0156389316914</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>12</v>
@@ -1507,22 +1489,22 @@
     </row>
     <row r="20" spans="2:9" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>44</v>
-      </c>
       <c r="D20" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E20" s="14">
-        <v>19236330</v>
+        <v>13336330</v>
       </c>
       <c r="F20" s="15">
-        <v>1619.70</v>
+        <v>1226.94</v>
       </c>
       <c r="G20" s="16">
-        <v>0.0145964151793</v>
+        <v>0.0107224455996</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>12</v>
@@ -1533,22 +1515,22 @@
     </row>
     <row r="21" spans="2:9" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>46</v>
-      </c>
       <c r="D21" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E21" s="14">
-        <v>1854880</v>
+        <v>8932511.524</v>
       </c>
       <c r="F21" s="15">
-        <v>1596.31</v>
+        <v>1074.91</v>
       </c>
       <c r="G21" s="16">
-        <v>0.014385629138</v>
+        <v>0.0093938285486</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>12</v>
@@ -1559,22 +1541,22 @@
     </row>
     <row r="22" spans="2:9" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>48</v>
-      </c>
       <c r="D22" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E22" s="14">
-        <v>2758080</v>
+        <v>880500</v>
       </c>
       <c r="F22" s="15">
-        <v>1267.06</v>
+        <v>806.19</v>
       </c>
       <c r="G22" s="16">
-        <v>0.0114184934352</v>
+        <v>0.0070454369553</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>12</v>
@@ -1585,58 +1567,58 @@
     </row>
     <row r="23" spans="2:9" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="15" customHeight="1">
+      <c r="B24" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="9">
+        <v>33040.16</v>
+      </c>
+      <c r="G24" s="10">
+        <v>0.2887438001886</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="15" customHeight="1">
+      <c r="B25" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C25" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="14">
-        <v>8932511.524</v>
-      </c>
-      <c r="F23" s="15">
-        <v>1041.40</v>
-      </c>
-      <c r="G23" s="16">
-        <v>0.0093848902684</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" ht="15" customHeight="1">
-      <c r="B24" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" ht="15" customHeight="1">
-      <c r="B25" s="7" t="s">
+      <c r="D25" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="9">
-        <v>32562.66</v>
-      </c>
-      <c r="G25" s="10">
-        <v>0.2934482340573</v>
-      </c>
-      <c r="H25" s="9" t="s">
+      <c r="E25" s="14">
+        <v>82850</v>
+      </c>
+      <c r="F25" s="15">
+        <v>5247.64</v>
+      </c>
+      <c r="G25" s="16">
+        <v>0.045860053814</v>
+      </c>
+      <c r="H25" s="15" t="s">
         <v>12</v>
       </c>
       <c r="I25" s="11" t="s">
@@ -1651,16 +1633,16 @@
         <v>53</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E26" s="14">
-        <v>118481</v>
+        <v>106281</v>
       </c>
       <c r="F26" s="15">
-        <v>4969.46</v>
+        <v>4798.52</v>
       </c>
       <c r="G26" s="16">
-        <v>0.0447837879713</v>
+        <v>0.0419351147235</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>12</v>
@@ -1671,22 +1653,22 @@
     </row>
     <row r="27" spans="2:9" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="E27" s="14">
-        <v>82850</v>
+        <v>64610</v>
       </c>
       <c r="F27" s="15">
-        <v>4903.46</v>
+        <v>3716.79</v>
       </c>
       <c r="G27" s="16">
-        <v>0.0441890090605</v>
+        <v>0.0324816849889</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>12</v>
@@ -1703,16 +1685,16 @@
         <v>58</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E28" s="14">
-        <v>64610</v>
+        <v>91455</v>
       </c>
       <c r="F28" s="15">
-        <v>3437.11</v>
+        <v>3350.53</v>
       </c>
       <c r="G28" s="16">
-        <v>0.0309745536686</v>
+        <v>0.0292808740892</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>12</v>
@@ -1723,22 +1705,22 @@
     </row>
     <row r="29" spans="2:9" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>61</v>
-      </c>
       <c r="D29" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E29" s="14">
-        <v>38501</v>
+        <v>154143</v>
       </c>
       <c r="F29" s="15">
-        <v>3413.17</v>
+        <v>3330.84</v>
       </c>
       <c r="G29" s="16">
-        <v>0.0307588111364</v>
+        <v>0.0291087996977</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>12</v>
@@ -1749,22 +1731,22 @@
     </row>
     <row r="30" spans="2:9" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="D30" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E30" s="14">
-        <v>91455</v>
+        <v>38501</v>
       </c>
       <c r="F30" s="15">
-        <v>3080.77</v>
+        <v>3302.50</v>
       </c>
       <c r="G30" s="16">
-        <v>0.0277632882583</v>
+        <v>0.0288611314268</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>12</v>
@@ -1775,22 +1757,22 @@
     </row>
     <row r="31" spans="2:9" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>65</v>
-      </c>
       <c r="D31" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E31" s="14">
-        <v>154143</v>
+        <v>61760</v>
       </c>
       <c r="F31" s="15">
-        <v>3066.35</v>
+        <v>2673.87</v>
       </c>
       <c r="G31" s="16">
-        <v>0.0276333380781</v>
+        <v>0.0233674227065</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>12</v>
@@ -1801,22 +1783,22 @@
     </row>
     <row r="32" spans="2:9" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>67</v>
-      </c>
       <c r="D32" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E32" s="14">
-        <v>69460</v>
+        <v>34942</v>
       </c>
       <c r="F32" s="15">
-        <v>2344.66</v>
+        <v>2159.43</v>
       </c>
       <c r="G32" s="16">
-        <v>0.0211296109244</v>
+        <v>0.0188716405865</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>12</v>
@@ -1827,22 +1809,22 @@
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="D33" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E33" s="14">
-        <v>34942</v>
+        <v>55928</v>
       </c>
       <c r="F33" s="15">
-        <v>2096.49</v>
+        <v>1940.92</v>
       </c>
       <c r="G33" s="16">
-        <v>0.0188931521018</v>
+        <v>0.016962043061</v>
       </c>
       <c r="H33" s="15" t="s">
         <v>12</v>
@@ -1853,22 +1835,22 @@
     </row>
     <row r="34" spans="2:9" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>71</v>
-      </c>
       <c r="D34" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E34" s="14">
-        <v>55928</v>
+        <v>12675</v>
       </c>
       <c r="F34" s="15">
-        <v>1981.40</v>
+        <v>929.69</v>
       </c>
       <c r="G34" s="16">
-        <v>0.0178559838466</v>
+        <v>0.0081247252918</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>12</v>
@@ -1879,22 +1861,22 @@
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>73</v>
-      </c>
       <c r="D35" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E35" s="14">
-        <v>12675</v>
+        <v>15750</v>
       </c>
       <c r="F35" s="15">
-        <v>1013.62</v>
+        <v>510.91</v>
       </c>
       <c r="G35" s="16">
-        <v>0.0091345424177</v>
+        <v>0.0044649328258</v>
       </c>
       <c r="H35" s="15" t="s">
         <v>12</v>
@@ -1905,22 +1887,22 @@
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="D36" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E36" s="14">
-        <v>7050</v>
+        <v>3877</v>
       </c>
       <c r="F36" s="15">
-        <v>623.80</v>
+        <v>403.38</v>
       </c>
       <c r="G36" s="16">
-        <v>0.0056215618873</v>
+        <v>0.003525209143</v>
       </c>
       <c r="H36" s="15" t="s">
         <v>12</v>
@@ -1931,22 +1913,22 @@
     </row>
     <row r="37" spans="2:9" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>77</v>
-      </c>
       <c r="D37" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E37" s="14">
-        <v>15750</v>
+        <v>7000</v>
       </c>
       <c r="F37" s="15">
-        <v>533.08</v>
+        <v>393.23</v>
       </c>
       <c r="G37" s="16">
-        <v>0.0048040112389</v>
+        <v>0.0034365064984</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>12</v>
@@ -1957,22 +1939,22 @@
     </row>
     <row r="38" spans="2:9" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="D38" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E38" s="14">
-        <v>3877</v>
+        <v>6480</v>
       </c>
       <c r="F38" s="15">
-        <v>465.77</v>
+        <v>281.91</v>
       </c>
       <c r="G38" s="16">
-        <v>0.0041974268679</v>
+        <v>0.0024636613355</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>12</v>
@@ -1983,22 +1965,22 @@
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="D39" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="14">
+        <v>12275</v>
+      </c>
+      <c r="F39" s="15">
+        <v>0</v>
+      </c>
+      <c r="G39" s="17" t="s">
         <v>81</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="14">
-        <v>7000</v>
-      </c>
-      <c r="F39" s="15">
-        <v>348.31</v>
-      </c>
-      <c r="G39" s="16">
-        <v>0.0031389006427</v>
       </c>
       <c r="H39" s="15" t="s">
         <v>12</v>
@@ -2009,50 +1991,32 @@
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" ht="15" customHeight="1">
+      <c r="B41" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E40" s="14">
-        <v>6480</v>
-      </c>
-      <c r="F40" s="15">
-        <v>285.21</v>
-      </c>
-      <c r="G40" s="16">
-        <v>0.0025702559568</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I40" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" ht="15" customHeight="1">
-      <c r="B41" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41" s="14">
-        <v>12275</v>
-      </c>
-      <c r="F41" s="15">
-        <v>0</v>
-      </c>
-      <c r="G41" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H41" s="15" t="s">
+      <c r="C41" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="9">
+        <v>5363.52</v>
+      </c>
+      <c r="G41" s="10">
+        <v>0.0468727496231</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I41" s="11" t="s">
@@ -2068,105 +2032,89 @@
       </c>
     </row>
     <row r="43" spans="2:9" ht="15" customHeight="1">
-      <c r="B43" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" s="9">
-        <v>2616.84</v>
-      </c>
-      <c r="G43" s="10">
-        <v>0.0235824431054</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I43" s="11" t="s">
+      <c r="B43" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="19">
+        <v>-1030.116571999999</v>
+      </c>
+      <c r="G43" s="20">
+        <v>-0.009002370861310324</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="I43" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1">
-      <c r="B44" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I44" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" ht="15" customHeight="1">
-      <c r="B45" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" s="19">
-        <v>1035.3321768999886</v>
-      </c>
-      <c r="G45" s="20">
-        <v>0.009330208250025757</v>
-      </c>
-      <c r="H45" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" ht="15" customHeight="1">
-      <c r="B46" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="19">
-        <v>110965.6021769</v>
-      </c>
-      <c r="G46" s="20">
-        <v>0.9999999999982256</v>
-      </c>
-      <c r="H46" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>12</v>
+      <c r="B44" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="19">
+        <v>114427.253428</v>
+      </c>
+      <c r="G44" s="20">
+        <v>0.9999999999986898</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="B47" s="13" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="B49" s="13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="B51" s="13" t="s">
-        <v>91</v>
-      </c>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B51" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="22"/>
+    </row>
+    <row r="52" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B53" s="21" t="s">
-        <v>92</v>
-      </c>
+      <c r="B53" s="22"/>
       <c r="C53" s="22"/>
       <c r="D53" s="22"/>
       <c r="E53" s="22"/>
@@ -2201,57 +2149,34 @@
       <c r="G56" s="22"/>
       <c r="H56" s="22"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-    </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="B60" s="13" t="s">
-        <v>93</v>
+    <row r="58" ht="15" customHeight="1">
+      <c r="B58" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="59" ht="27.5" customHeight="1">
+      <c r="B59" s="23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60" ht="27.5" customHeight="1">
+      <c r="B60" s="23" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="61" ht="27.5" customHeight="1">
       <c r="B61" s="23" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="62" ht="27.5" customHeight="1">
-      <c r="B62" s="23" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="63" ht="27.5" customHeight="1">
-      <c r="B63" s="23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="66" ht="15">
-      <c r="B66" s="24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="81" ht="15">
-      <c r="B81" s="24" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="82" ht="15">
-      <c r="B82" s="24" t="s">
-        <v>99</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="64" ht="15">
+      <c r="B64" s="24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="79" ht="15">
+      <c r="B79" s="24" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2259,13 +2184,13 @@
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B47:H47"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B51:H51"/>
-    <mergeCell ref="B53:H58"/>
+    <mergeCell ref="B51:H56"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B59:H59"/>
     <mergeCell ref="B60:H60"/>
     <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="B63:H63"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
